--- a/dataset/review result/c_result_gpt-4-turbo-preview_2024-04-06 18_09_25.xlsx
+++ b/dataset/review result/c_result_gpt-4-turbo-preview_2024-04-06 18_09_25.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oywy2\Desktop\增补数据校验\增补数据校验\【增补review数据集】\C\补充\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\LLM-CMT\dataset\review result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C03D14-CA45-4120-A82C-C15A7F263AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FDA033-047D-402E-868A-6335328E5879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36790" yWindow="-5940" windowWidth="28800" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-33570" yWindow="6675" windowWidth="28635" windowHeight="9765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="c_result_gpt-4-turbo-preview_20" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="c_result_gpt-4-turbo-preview_20" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="6" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="288">
   <si>
     <t>absolute_path</t>
   </si>
@@ -888,6 +892,15 @@
   </si>
   <si>
     <t>Unrecognized misuse</t>
+  </si>
+  <si>
+    <t>行标签</t>
+  </si>
+  <si>
+    <t>(空白)</t>
+  </si>
+  <si>
+    <t>总计</t>
   </si>
 </sst>
 </file>
@@ -895,7 +908,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="yyyy/m/d\ h:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d\ h:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -929,9 +942,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1160,6 +1177,653 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="欧阳文宜" refreshedDate="45445.675749421294" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="100" xr:uid="{2650E5DB-4E11-4918-95BB-FC3D47762371}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="B1:B1048576" sheet="c_result_gpt-4-turbo-preview_20"/>
+  </cacheSource>
+  <cacheFields count="1">
+    <cacheField name="filename" numFmtId="0">
+      <sharedItems containsBlank="1" count="58">
+        <s v="189aes_core.c"/>
+        <s v="189c_zlib.c"/>
+        <s v="189c_allc.c"/>
+        <s v="189ciphers.c"/>
+        <s v="189cbc128.c"/>
+        <s v="189b_sock2.c"/>
+        <s v="189ca.c"/>
+        <s v="189buffer.c"/>
+        <s v="189by_dir.c"/>
+        <s v="189bss_bio.c"/>
+        <s v="189bss_file.c"/>
+        <s v="189bss_log.c"/>
+        <s v="189bn_rand.c"/>
+        <s v="189bn_srp.c"/>
+        <s v="189bn_x931p.c"/>
+        <s v="189bn_lib.c"/>
+        <s v="189bn_print.c"/>
+        <s v="189bn_depr.c"/>
+        <s v="189bn_dh.c"/>
+        <s v="189bn_div.c"/>
+        <s v="189asn_mime.c"/>
+        <s v="189bio_ok.c"/>
+        <s v="189bn_blind.c"/>
+        <s v="189bio_ssl.c"/>
+        <s v="189bio_ndef.c"/>
+        <s v="189bio_enc.c"/>
+        <s v="189bio_lib.c"/>
+        <s v="189bio_b64.c"/>
+        <s v="189bf_ofb64.c"/>
+        <s v="189bf_skey.c"/>
+        <s v="189bf_enc.c"/>
+        <s v="189bf_nbio.c"/>
+        <s v="189bf_cfb64.c"/>
+        <s v="189aes_ecb.c"/>
+        <s v="189bf_ecb.c"/>
+        <s v="189a_utctm.c"/>
+        <s v="189a_utf8.c"/>
+        <s v="189a_print.c"/>
+        <s v="189a_sign.c"/>
+        <s v="189aes_ofb.c"/>
+        <s v="189aes_wrap.c"/>
+        <s v="189aes_x86core.c"/>
+        <s v="189a_int.c"/>
+        <s v="189a_mbstr.c"/>
+        <s v="189a_object.c"/>
+        <s v="189a_dup.c"/>
+        <s v="189a_i2d_fp.c"/>
+        <s v="189async.c"/>
+        <s v="189a_gentm.c"/>
+        <s v="189asn_moid.c"/>
+        <s v="189asn_mstbl.c"/>
+        <s v="189a_bitstr.c"/>
+        <s v="189a_d2i_fp.c"/>
+        <s v="189a_digest.c"/>
+        <s v="189async_wait.c"/>
+        <s v="189asn_pack.c"/>
+        <s v="189aes_ige.c"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="100">
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="27"/>
+  </r>
+  <r>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="30"/>
+  </r>
+  <r>
+    <x v="31"/>
+  </r>
+  <r>
+    <x v="32"/>
+  </r>
+  <r>
+    <x v="33"/>
+  </r>
+  <r>
+    <x v="34"/>
+  </r>
+  <r>
+    <x v="35"/>
+  </r>
+  <r>
+    <x v="36"/>
+  </r>
+  <r>
+    <x v="37"/>
+  </r>
+  <r>
+    <x v="38"/>
+  </r>
+  <r>
+    <x v="38"/>
+  </r>
+  <r>
+    <x v="38"/>
+  </r>
+  <r>
+    <x v="39"/>
+  </r>
+  <r>
+    <x v="40"/>
+  </r>
+  <r>
+    <x v="41"/>
+  </r>
+  <r>
+    <x v="42"/>
+  </r>
+  <r>
+    <x v="43"/>
+  </r>
+  <r>
+    <x v="44"/>
+  </r>
+  <r>
+    <x v="45"/>
+  </r>
+  <r>
+    <x v="46"/>
+  </r>
+  <r>
+    <x v="47"/>
+  </r>
+  <r>
+    <x v="48"/>
+  </r>
+  <r>
+    <x v="46"/>
+  </r>
+  <r>
+    <x v="45"/>
+  </r>
+  <r>
+    <x v="48"/>
+  </r>
+  <r>
+    <x v="46"/>
+  </r>
+  <r>
+    <x v="49"/>
+  </r>
+  <r>
+    <x v="50"/>
+  </r>
+  <r>
+    <x v="51"/>
+  </r>
+  <r>
+    <x v="52"/>
+  </r>
+  <r>
+    <x v="53"/>
+  </r>
+  <r>
+    <x v="52"/>
+  </r>
+  <r>
+    <x v="53"/>
+  </r>
+  <r>
+    <x v="52"/>
+  </r>
+  <r>
+    <x v="53"/>
+  </r>
+  <r>
+    <x v="47"/>
+  </r>
+  <r>
+    <x v="54"/>
+  </r>
+  <r>
+    <x v="49"/>
+  </r>
+  <r>
+    <x v="50"/>
+  </r>
+  <r>
+    <x v="55"/>
+  </r>
+  <r>
+    <x v="49"/>
+  </r>
+  <r>
+    <x v="50"/>
+  </r>
+  <r>
+    <x v="55"/>
+  </r>
+  <r>
+    <x v="55"/>
+  </r>
+  <r>
+    <x v="39"/>
+  </r>
+  <r>
+    <x v="41"/>
+  </r>
+  <r>
+    <x v="56"/>
+  </r>
+  <r>
+    <x v="56"/>
+  </r>
+  <r>
+    <x v="57"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9CAF3E69-3A86-4C11-B14A-020026C59101}" name="数据透视表1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:A62" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="1">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="59">
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="45"/>
+        <item x="48"/>
+        <item x="46"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="0"/>
+        <item x="33"/>
+        <item x="56"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="20"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="55"/>
+        <item x="47"/>
+        <item x="54"/>
+        <item x="5"/>
+        <item x="32"/>
+        <item x="34"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="27"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="24"/>
+        <item x="21"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="57"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="59">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="54"/>
+    </i>
+    <i>
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pivotTableStyleInfo name="PivotStylePreset2_Accent1" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1419,16 +2083,330 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C9C1D9-510E-4524-8910-99B8A552F70C}">
+  <dimension ref="A3:A62"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M100"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.52734375" customWidth="1"/>
-    <col min="2" max="2" width="25.703125" customWidth="1"/>
-    <col min="6" max="6" width="60.9375" customWidth="1"/>
+    <col min="1" max="1" width="31.54296875" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" customWidth="1"/>
+    <col min="6" max="6" width="60.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1469,7 +2447,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1504,7 +2482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1539,7 +2517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1577,7 +2555,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1615,7 +2593,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1650,7 +2628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1688,7 +2666,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1726,7 +2704,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1764,7 +2742,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1802,7 +2780,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -1840,7 +2818,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1878,7 +2856,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1916,7 +2894,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -1951,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -1986,7 +2964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>50</v>
       </c>
@@ -2021,7 +2999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>54</v>
       </c>
@@ -2056,7 +3034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -2091,7 +3069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -2126,7 +3104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -2164,7 +3142,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>70</v>
       </c>
@@ -2202,7 +3180,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -2240,7 +3218,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>70</v>
       </c>
@@ -2278,7 +3256,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>78</v>
       </c>
@@ -2316,7 +3294,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>78</v>
       </c>
@@ -2354,7 +3332,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -2392,7 +3370,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>87</v>
       </c>
@@ -2427,7 +3405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -2462,7 +3440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -2497,7 +3475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>99</v>
       </c>
@@ -2535,7 +3513,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>91</v>
       </c>
@@ -2573,7 +3551,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>95</v>
       </c>
@@ -2611,7 +3589,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>99</v>
       </c>
@@ -2649,7 +3627,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>106</v>
       </c>
@@ -2684,7 +3662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>110</v>
       </c>
@@ -2722,7 +3700,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>110</v>
       </c>
@@ -2760,7 +3738,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>116</v>
       </c>
@@ -2795,7 +3773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>120</v>
       </c>
@@ -2833,7 +3811,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>124</v>
       </c>
@@ -2871,7 +3849,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>128</v>
       </c>
@@ -2906,7 +3884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>132</v>
       </c>
@@ -2941,7 +3919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>134</v>
       </c>
@@ -2976,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>134</v>
       </c>
@@ -3014,7 +3992,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>138</v>
       </c>
@@ -3052,7 +4030,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>142</v>
       </c>
@@ -3090,7 +4068,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>132</v>
       </c>
@@ -3128,7 +4106,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>142</v>
       </c>
@@ -3166,7 +4144,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>148</v>
       </c>
@@ -3204,7 +4182,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -3242,7 +4220,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>152</v>
       </c>
@@ -3280,7 +4258,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>158</v>
       </c>
@@ -3318,7 +4296,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>162</v>
       </c>
@@ -3353,7 +4331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>166</v>
       </c>
@@ -3391,7 +4369,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>170</v>
       </c>
@@ -3426,7 +4404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>174</v>
       </c>
@@ -3461,7 +4439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>178</v>
       </c>
@@ -3496,7 +4474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>182</v>
       </c>
@@ -3531,7 +4509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>186</v>
       </c>
@@ -3566,7 +4544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>188</v>
       </c>
@@ -3604,7 +4582,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>192</v>
       </c>
@@ -3642,7 +4620,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>196</v>
       </c>
@@ -3680,7 +4658,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>200</v>
       </c>
@@ -3715,7 +4693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>200</v>
       </c>
@@ -3753,7 +4731,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>200</v>
       </c>
@@ -3788,7 +4766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>208</v>
       </c>
@@ -3823,7 +4801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>210</v>
       </c>
@@ -3858,7 +4836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>212</v>
       </c>
@@ -3893,7 +4871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>214</v>
       </c>
@@ -3931,7 +4909,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>218</v>
       </c>
@@ -3969,7 +4947,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>222</v>
       </c>
@@ -4007,7 +4985,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>226</v>
       </c>
@@ -4045,7 +5023,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>230</v>
       </c>
@@ -4083,7 +5061,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>232</v>
       </c>
@@ -4121,7 +5099,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>234</v>
       </c>
@@ -4159,7 +5137,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>230</v>
       </c>
@@ -4197,7 +5175,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>226</v>
       </c>
@@ -4235,7 +5213,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>234</v>
       </c>
@@ -4273,7 +5251,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>230</v>
       </c>
@@ -4311,7 +5289,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>242</v>
       </c>
@@ -4346,7 +5324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>244</v>
       </c>
@@ -4381,7 +5359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>246</v>
       </c>
@@ -4419,7 +5397,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>250</v>
       </c>
@@ -4457,7 +5435,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>252</v>
       </c>
@@ -4495,7 +5473,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>250</v>
       </c>
@@ -4530,7 +5508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>252</v>
       </c>
@@ -4565,7 +5543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>250</v>
       </c>
@@ -4603,7 +5581,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>252</v>
       </c>
@@ -4638,7 +5616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>232</v>
       </c>
@@ -4676,7 +5654,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>262</v>
       </c>
@@ -4714,7 +5692,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>242</v>
       </c>
@@ -4752,7 +5730,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>244</v>
       </c>
@@ -4790,7 +5768,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>268</v>
       </c>
@@ -4828,7 +5806,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>242</v>
       </c>
@@ -4866,7 +5844,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>244</v>
       </c>
@@ -4904,7 +5882,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>268</v>
       </c>
@@ -4942,7 +5920,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>268</v>
       </c>
@@ -4980,7 +5958,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>208</v>
       </c>
@@ -5015,7 +5993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>212</v>
       </c>
@@ -5053,7 +6031,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>278</v>
       </c>
@@ -5091,7 +6069,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>278</v>
       </c>
